--- a/GOOGLE_ADS_LAUNCH_PACK.xlsx
+++ b/GOOGLE_ADS_LAUNCH_PACK.xlsx
@@ -392,7 +392,7 @@
     <t>Call extension</t>
   </si>
   <si>
-    <t>+971 58 108 2601</t>
+    <t>+971 55 540 3038</t>
   </si>
   <si>
     <t>Location extension</t>
